--- a/src/test/resources/testData/phoenix_test_data.xlsx
+++ b/src/test/resources/testData/phoenix_test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanagash\eclipse-workspace\PhoenixApiTestAutomation\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97D7BC0-08B3-4CE6-973C-738C27BC3431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE41E2BE-9A2A-4FA8-A47B-FE90F69F96AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
   <si>
     <t>username</t>
   </si>
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
@@ -390,38 +390,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testData/phoenix_test_data.xlsx
+++ b/src/test/resources/testData/phoenix_test_data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanagash\eclipse-workspace\PhoenixApiTestAutomation\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE41E2BE-9A2A-4FA8-A47B-FE90F69F96AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B81379-1393-4E92-8AE4-08BE3E9119E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginTestData" sheetId="1" r:id="rId1"/>
+    <sheet name="createJobTestData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>username</t>
   </si>
@@ -34,16 +35,147 @@
   </si>
   <si>
     <t>iamfd</t>
+  </si>
+  <si>
+    <t>mst_service_location_id</t>
+  </si>
+  <si>
+    <t>mst_platform_id</t>
+  </si>
+  <si>
+    <t>mst_warrenty_status_id</t>
+  </si>
+  <si>
+    <t>mst_oem_id</t>
+  </si>
+  <si>
+    <t>customer__first_name</t>
+  </si>
+  <si>
+    <t>customer__last_name</t>
+  </si>
+  <si>
+    <t>customer__mobile_number</t>
+  </si>
+  <si>
+    <t>customer__mobile_number_alt</t>
+  </si>
+  <si>
+    <t>customer__email_id</t>
+  </si>
+  <si>
+    <t>customer__email_id_alt</t>
+  </si>
+  <si>
+    <t>customer_address__flat_number</t>
+  </si>
+  <si>
+    <t>customer_address__apartment_name</t>
+  </si>
+  <si>
+    <t>customer_address__street_name</t>
+  </si>
+  <si>
+    <t>customer_address__landmark</t>
+  </si>
+  <si>
+    <t>customer_address__area</t>
+  </si>
+  <si>
+    <t>customer_address__pincode</t>
+  </si>
+  <si>
+    <t>customer_address__country</t>
+  </si>
+  <si>
+    <t>customer_address__state</t>
+  </si>
+  <si>
+    <t>customer_product__dop</t>
+  </si>
+  <si>
+    <t>customer_product__serial_number</t>
+  </si>
+  <si>
+    <t>customer_product__imei1</t>
+  </si>
+  <si>
+    <t>customer_product__imei2</t>
+  </si>
+  <si>
+    <t>customer_product__popurl</t>
+  </si>
+  <si>
+    <t>customer_product__product_id</t>
+  </si>
+  <si>
+    <t>customer_product__mst_model_id</t>
+  </si>
+  <si>
+    <t>problems__id</t>
+  </si>
+  <si>
+    <t>problems__remark</t>
+  </si>
+  <si>
+    <t>Mani</t>
+  </si>
+  <si>
+    <t>Somayaji</t>
+  </si>
+  <si>
+    <t>vidhur.patil@hotmail.com</t>
+  </si>
+  <si>
+    <t>A-997</t>
+  </si>
+  <si>
+    <t>Kakkar Crossing</t>
+  </si>
+  <si>
+    <t>Aadrika Junction</t>
+  </si>
+  <si>
+    <t>Chandraketu Course</t>
+  </si>
+  <si>
+    <t>85321 Bilva Cliff</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Daman and Diu</t>
+  </si>
+  <si>
+    <t>2025-12-18T17:24:14.956774600Z</t>
+  </si>
+  <si>
+    <t>ww.advaya-sinha.in</t>
+  </si>
+  <si>
+    <t>Ut illum autem</t>
+  </si>
+  <si>
+    <t>235601162186240</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,13 +198,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -393,4 +536,219 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB93E7C-1E3C-4923-9B00-59B55DB14AB9}">
+  <dimension ref="A1:AA4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" customWidth="1"/>
+    <col min="6" max="6" width="23.36328125" customWidth="1"/>
+    <col min="7" max="7" width="25.81640625" customWidth="1"/>
+    <col min="8" max="8" width="28.81640625" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.90625" customWidth="1"/>
+    <col min="11" max="11" width="30.90625" customWidth="1"/>
+    <col min="12" max="12" width="33.08984375" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="14" max="14" width="28.1796875" customWidth="1"/>
+    <col min="15" max="15" width="23.6328125" customWidth="1"/>
+    <col min="16" max="16" width="28" customWidth="1"/>
+    <col min="17" max="17" width="23.453125" customWidth="1"/>
+    <col min="18" max="18" width="13.453125" customWidth="1"/>
+    <col min="19" max="19" width="28.08984375" customWidth="1"/>
+    <col min="20" max="20" width="38.26953125" customWidth="1"/>
+    <col min="21" max="22" width="25.7265625" customWidth="1"/>
+    <col min="23" max="23" width="27.453125" customWidth="1"/>
+    <col min="24" max="24" width="30.90625" customWidth="1"/>
+    <col min="25" max="25" width="38.90625" customWidth="1"/>
+    <col min="26" max="26" width="20.6328125" customWidth="1"/>
+    <col min="27" max="27" width="17.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1">
+        <v>7747300092</v>
+      </c>
+      <c r="H2" s="1">
+        <v>7747300082</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1">
+        <v>95703</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>12</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="W2" r:id="rId1" display="www.advaya-sinha.in" xr:uid="{8954B304-508C-43C3-9F0F-61331272973F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testData/phoenix_test_data.xlsx
+++ b/src/test/resources/testData/phoenix_test_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanagash\eclipse-workspace\PhoenixApiTestAutomation\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B81379-1393-4E92-8AE4-08BE3E9119E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760FCA73-6745-492B-9B43-004CC9426DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>username</t>
   </si>
@@ -157,7 +157,37 @@
     <t>Ut illum autem</t>
   </si>
   <si>
-    <t>235601162186240</t>
+    <t>dhoni</t>
+  </si>
+  <si>
+    <t>mahendra</t>
+  </si>
+  <si>
+    <t>dhoni@hotmail.com</t>
+  </si>
+  <si>
+    <t>A-100</t>
+  </si>
+  <si>
+    <t>whisling Crossing</t>
+  </si>
+  <si>
+    <t>mankar Junction</t>
+  </si>
+  <si>
+    <t>BRT STOP</t>
+  </si>
+  <si>
+    <t>Kaspate wasti</t>
+  </si>
+  <si>
+    <t>india</t>
+  </si>
+  <si>
+    <t>battery iaaue</t>
+  </si>
+  <si>
+    <t>23561102186240</t>
   </si>
 </sst>
 </file>
@@ -551,7 +581,7 @@
     <col min="6" max="6" width="23.36328125" customWidth="1"/>
     <col min="7" max="7" width="25.81640625" customWidth="1"/>
     <col min="8" max="8" width="28.81640625" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="9" max="9" width="26.26953125" customWidth="1"/>
     <col min="10" max="10" width="21.90625" customWidth="1"/>
     <col min="11" max="11" width="30.90625" customWidth="1"/>
     <col min="12" max="12" width="33.08984375" customWidth="1"/>
@@ -679,10 +709,10 @@
       <c r="H2" s="1">
         <v>7747300082</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -713,13 +743,13 @@
         <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>41</v>
@@ -738,8 +768,87 @@
       </c>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="1">
+        <v>7747300123</v>
+      </c>
+      <c r="H3" s="1">
+        <v>7747300123</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="1">
+        <v>95790</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>12</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="T4" s="2"/>
@@ -748,6 +857,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="W2" r:id="rId1" display="www.advaya-sinha.in" xr:uid="{8954B304-508C-43C3-9F0F-61331272973F}"/>
+    <hyperlink ref="W3" r:id="rId2" display="www.advaya-sinha.in" xr:uid="{46E17A9F-C5DC-4672-BAAE-1E295D7A58BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testData/phoenix_test_data.xlsx
+++ b/src/test/resources/testData/phoenix_test_data.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanagash\eclipse-workspace\PhoenixApiTestAutomation\src\test\resources\testData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760FCA73-6745-492B-9B43-004CC9426DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{4658AC05-D8E8-4840-AD67-3CCF872D3865}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15285" windowHeight="5895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginTestData" sheetId="1" r:id="rId1"/>
     <sheet name="createJobTestData" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:O17"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -525,13 +521,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -547,7 +543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -555,7 +551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -571,37 +567,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB93E7C-1E3C-4923-9B00-59B55DB14AB9}">
   <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.36328125" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="23.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
-    <col min="5" max="5" width="20.54296875" customWidth="1"/>
-    <col min="6" max="6" width="23.36328125" customWidth="1"/>
-    <col min="7" max="7" width="25.81640625" customWidth="1"/>
-    <col min="8" max="8" width="28.81640625" customWidth="1"/>
-    <col min="9" max="9" width="26.26953125" customWidth="1"/>
-    <col min="10" max="10" width="21.90625" customWidth="1"/>
-    <col min="11" max="11" width="30.90625" customWidth="1"/>
-    <col min="12" max="12" width="33.08984375" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="30.85546875" customWidth="1"/>
+    <col min="12" max="12" width="33.140625" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="14" width="28.1796875" customWidth="1"/>
-    <col min="15" max="15" width="23.6328125" customWidth="1"/>
+    <col min="14" max="14" width="28.140625" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" customWidth="1"/>
     <col min="16" max="16" width="28" customWidth="1"/>
-    <col min="17" max="17" width="23.453125" customWidth="1"/>
-    <col min="18" max="18" width="13.453125" customWidth="1"/>
-    <col min="19" max="19" width="28.08984375" customWidth="1"/>
-    <col min="20" max="20" width="38.26953125" customWidth="1"/>
-    <col min="21" max="22" width="25.7265625" customWidth="1"/>
-    <col min="23" max="23" width="27.453125" customWidth="1"/>
-    <col min="24" max="24" width="30.90625" customWidth="1"/>
-    <col min="25" max="25" width="38.90625" customWidth="1"/>
-    <col min="26" max="26" width="20.6328125" customWidth="1"/>
-    <col min="27" max="27" width="17.7265625" customWidth="1"/>
+    <col min="17" max="17" width="23.42578125" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1"/>
+    <col min="19" max="19" width="28.140625" customWidth="1"/>
+    <col min="20" max="20" width="38.28515625" customWidth="1"/>
+    <col min="21" max="22" width="25.7109375" customWidth="1"/>
+    <col min="23" max="23" width="27.42578125" customWidth="1"/>
+    <col min="24" max="24" width="30.85546875" customWidth="1"/>
+    <col min="25" max="25" width="38.85546875" customWidth="1"/>
+    <col min="26" max="26" width="20.5703125" customWidth="1"/>
+    <col min="27" max="27" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -684,7 +680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -767,7 +763,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -850,7 +846,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
